--- a/errors_dict.xlsx
+++ b/errors_dict.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Моделі</t>
   </si>
@@ -73,6 +73,42 @@
     <t xml:space="preserve">08_</t>
   </si>
   <si>
+    <t xml:space="preserve">01_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пробіг не може бути меншим за нуль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Новий пробіг не може бути меншим за попередній</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фізична особа обов'язково має мати ідентифікаційний код</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФОП обов'язково має мати ідентифікаційний код</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Компанія обов'язково має мати ЄРДПОУ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Компанія повинна мати представника</t>
+  </si>
+  <si>
     <t xml:space="preserve">06_01</t>
   </si>
   <si>
@@ -112,22 +148,16 @@
     <t xml:space="preserve">06_07</t>
   </si>
   <si>
-    <t xml:space="preserve">Транспорт потребує ТО/Ремонту або вже знаходиться на ТО/Ремонті</t>
+    <t xml:space="preserve">Замовлення вже доставляється</t>
   </si>
   <si>
     <t xml:space="preserve">06_08</t>
   </si>
   <si>
-    <t xml:space="preserve">Замовлення вже доставляється</t>
+    <t xml:space="preserve">Замовлення вже виконане</t>
   </si>
   <si>
     <t xml:space="preserve">06_09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Замовлення вже виконане</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_10</t>
   </si>
   <si>
     <t xml:space="preserve">Не можливо змінити замовлення під час поїздки</t>
@@ -166,6 +196,7 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -210,7 +241,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -219,15 +250,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -354,11 +389,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -431,83 +466,139 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0"/>
+      <c r="B20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B28" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/errors_dict.xlsx
+++ b/errors_dict.xlsx
@@ -20,11 +20,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t xml:space="preserve">Моделі</t>
   </si>
   <si>
+    <t xml:space="preserve">Загальні помилки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00_</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transport</t>
   </si>
   <si>
@@ -73,6 +79,12 @@
     <t xml:space="preserve">08_</t>
   </si>
   <si>
+    <t xml:space="preserve">00_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Значення не може бути меншим за 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">01_01</t>
   </si>
   <si>
@@ -85,6 +97,24 @@
     <t xml:space="preserve">Новий пробіг не може бути меншим за попередній</t>
   </si>
   <si>
+    <t xml:space="preserve">02_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Водій з цим номером телефону вже існує</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Водій з цим посвідченням вже існує</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Водій з цим ІПН вже існує</t>
+  </si>
+  <si>
     <t xml:space="preserve">03_01</t>
   </si>
   <si>
@@ -107,6 +137,36 @@
   </si>
   <si>
     <t xml:space="preserve">Компанія повинна мати представника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Клієнт з цим номером телефону вже існує</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Клієнт з цією поштою вже існує</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Клієнт з цим ІПН вже існує</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Компанія з цим ЄДРПОУ вже існує</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Замовлення з цим айді оплати вже існує</t>
   </si>
   <si>
     <t xml:space="preserve">06_01</t>
@@ -241,7 +301,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -254,16 +314,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -389,11 +445,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -405,7 +461,7 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -465,28 +521,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -494,111 +546,206 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0"/>
-      <c r="B19" s="0"/>
-    </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0"/>
-      <c r="B20" s="0"/>
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>34</v>
+      <c r="A28" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>36</v>
+      <c r="A29" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="A30" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0"/>
+      <c r="B31" s="0"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>42</v>
+      <c r="A32" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>46</v>
+      <c r="A33" s="0"/>
+      <c r="B33" s="0"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0"/>
+      <c r="B35" s="0"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0"/>
+      <c r="B36" s="0"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0"/>
+      <c r="B37" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
